--- a/Texte/Textbausteine_LENA_Maerz2026.xlsx
+++ b/Texte/Textbausteine_LENA_Maerz2026.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="554">
   <si>
     <t>Kanton</t>
   </si>
@@ -218,7 +218,7 @@
     <t>GE</t>
   </si>
   <si>
-    <t>Loi modifiant la loi sur l'inspection et les relations du travail (LIRT)</t>
+    <t>Exclusion des jobs d'été du salaire minimum</t>
   </si>
   <si>
     <t>BL</t>
@@ -335,7 +335,7 @@
     <t>È stata approvata col #JaStimmenHauptvorlageInProzent % l'Iniziativa sul denaro contante. Sì con il #JaStimmenGegenvorschlagInProzent % anche al controprogetto. I cittadini di #Gemeinde_i hanno però preferito il controprogetto con il #StichentscheidZustimmungHauptvorlageInProzent % .</t>
   </si>
   <si>
-    <t>Die Stimmberechtigten in #Gemeinde_d haben die Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent an angenommen und befürworten auch den Gegenvorschlag von Bundesrat und Parlament mit \#JaStimmenGegenvorschlagInProzent Prozent. Das Resultat der Stichfrage ergab mit #StichentscheidZustimmungGegenvorschlagInProzent Prozent den Vorzug für den Gegenvorschlag.</t>
+    <t>Die Stimmberechtigten in #Gemeinde_d haben die Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent an angenommen und befürworten auch den Gegenvorschlag von Bundesrat und Parlament mit #JaStimmenGegenvorschlagInProzent Prozent. Das Resultat der Stichfrage ergab mit #StichentscheidZustimmungGegenvorschlagInProzent Prozent den Vorzug für den Gegenvorschlag.</t>
   </si>
   <si>
     <t>Les citoyens de #Gemeinde_f privilégient le contre-projet du Conseil fédéral et du Parlement, qui vise à garantir la disponibilité de l'argent liquide (#StichentscheidZustimmungGegenvorschlagInProzent % de oui à la question subsidiaire). Le texte recueille #JaStimmenGegenvorschlagInProzent % de oui. L'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" est toutefois également acceptée avec #JaStimmenHauptvorlageInProzent % de oui.</t>
@@ -815,6 +815,9 @@
     <t>Damit ist in #Gemeinde_d die Ablehnung im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 ungefähr gleich geblieten.</t>
   </si>
   <si>
+    <t>Le rejet de l'initiative dimanche à #Gemeinde_f est proche à celui de l'initiative No Billag en 2018.</t>
+  </si>
+  <si>
     <t>La quota di no a #Gemeinde_i è rimasta pressoché invariata rispetto alla votazione sull'iniziativa No-Billag del 2018.</t>
   </si>
   <si>
@@ -827,6 +830,9 @@
     <t>Erstaunlicherweise ist damit der Nein-Stimmen-Anteil in #Gemeinde_d im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 genau gleich geblieben.</t>
   </si>
   <si>
+    <t>Fait étonnant: le pourcentage de non à l'initiative dimanche à #Gemeinde_f est identique à celui de l'initiative No Billag en 2018.</t>
+  </si>
+  <si>
     <t>Sorprendentemente, la quota di no a #Gemeinde_i è rimasta esattamente la stessa rispetto alla votazione sull'iniziativa No-Billag del 2018.</t>
   </si>
   <si>
@@ -836,7 +842,10 @@
     <t>HistoricPhrase_Nein_Ja</t>
   </si>
   <si>
-    <t>Damit hat in #Gemeinde_d seit der letzten Abstimmung über die Erbschaftssteuer im Jahr 2018 ein Meinungsumschwung stattgefunden: Damals hatte noch eine Mehrheit von #HistNeinStimmenInProzent Prozent ein Nein in die Urne gelegt.</t>
+    <t>Damit hat in #Gemeinde_d seit der letzten Abstimmung über die No-Billag-Initiative im Jahr 2018 ein Meinungsumschwung stattgefunden: Damals hatte noch eine Mehrheit von #HistNeinStimmenInProzent Prozent ein Nein in die Urne gelegt.</t>
+  </si>
+  <si>
+    <t>Changement d'opinion à #Gemeinde_f: en 2018, une majorité des habitants de la commune avait refusé l'initiative.</t>
   </si>
   <si>
     <t>A #Gemeinde_i c'è stato quindi un cambio di rotta rispetto all'ultima votazione sull'imposta di successione del 2018. All'epoca una maggioranza del #HistNeinStimmenInProzent per cento aveva votato no.</t>
@@ -851,6 +860,9 @@
     <t>Damit hat #Gemeinde_d seine Meinung im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 geändert: Damals hatte noch eine Mehrheit von #HistJaStimmenInProzent Prozent ein Ja in die Urne gelegt.</t>
   </si>
   <si>
+    <t>Changement d'opinion à #Gemeinde_f: en 2018, une majorité des habitants de la commune avait accepté l'initiative.</t>
+  </si>
+  <si>
     <t>#Gemeinde_i ha quindi cambiato opinione rispetto alla votazione sull'iniziativa No-Billag del 2018. All'epoca, infatti, una maggioranza del #HistJaStimmenInProzent per cento si era espressa a favore.</t>
   </si>
   <si>
@@ -861,6 +873,9 @@
   </si>
   <si>
     <t>Wegen der Veränderung der Gemeindestruktur ist ein Vergleich mit der Abstimmung von Juni 2021 über die Erbschaftssteuer in #Gemeinde_d nicht möglich.</t>
+  </si>
+  <si>
+    <t>Dans cette commune, impossible de comparer les résultats de dimanche avec ceux de l'initiative No Billag.</t>
   </si>
   <si>
     <t>A causa di modifiche territoriali, non è possibile fare un paragone con la votazione del giugno 2021 sull'imposta di successione a #Gemeinde_i.</t>
@@ -7944,7 +7959,7 @@
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="26" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3">
@@ -7953,7 +7968,7 @@
       </c>
       <c r="B3" s="50"/>
       <c r="C3" s="26" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4">
@@ -7962,7 +7977,7 @@
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="26" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5">
@@ -7971,7 +7986,7 @@
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="26" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6">
@@ -7980,7 +7995,7 @@
       </c>
       <c r="B6" s="35"/>
       <c r="C6" s="26" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7">
@@ -7989,7 +8004,7 @@
       </c>
       <c r="B7" s="35"/>
       <c r="C7" s="26" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
@@ -7998,7 +8013,7 @@
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="26" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9">
@@ -8007,7 +8022,7 @@
       </c>
       <c r="B9" s="35"/>
       <c r="C9" s="26" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10">
@@ -8016,7 +8031,7 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="26" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11">
@@ -8025,7 +8040,7 @@
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="26" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12">
@@ -8034,61 +8049,61 @@
       </c>
       <c r="B12" s="35"/>
       <c r="C12" s="26" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="40" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="35"/>
       <c r="C13" s="26" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="40" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="35"/>
       <c r="C14" s="26" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="35"/>
       <c r="C15" s="26" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="35"/>
       <c r="C16" s="26" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="42" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="35"/>
       <c r="C17" s="26" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="42" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="26" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -8228,7 +8243,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -8237,7 +8252,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -8246,7 +8261,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8255,7 +8270,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -8264,7 +8279,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -8273,7 +8288,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -20130,7 +20145,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -20139,7 +20154,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -20148,7 +20163,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -20157,7 +20172,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -20166,7 +20181,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -20175,7 +20190,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -25970,47 +25985,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="55" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B1" s="56" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="45" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="45" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="45" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="45" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="45" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B6" s="57">
         <v>60.4</v>
@@ -26018,7 +26033,7 @@
     </row>
     <row r="7">
       <c r="A7" s="45" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B7" s="57">
         <v>39.6</v>
@@ -26026,23 +26041,23 @@
     </row>
     <row r="8">
       <c r="A8" s="45" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="45" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="45" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B10" s="57">
         <v>60.4</v>
@@ -26050,7 +26065,7 @@
     </row>
     <row r="11">
       <c r="A11" s="45" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B11" s="57">
         <v>39.6</v>
@@ -26058,26 +26073,26 @@
     </row>
     <row r="12">
       <c r="A12" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="B12" s="57" t="s">
         <v>531</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="45" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="45" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15">
@@ -26085,13 +26100,13 @@
     </row>
     <row r="16">
       <c r="A16" s="59" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B16" s="58"/>
     </row>
     <row r="17">
       <c r="A17" s="45" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B17" s="57">
         <v>60.4</v>
@@ -26099,7 +26114,7 @@
     </row>
     <row r="18">
       <c r="A18" s="45" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B18" s="57">
         <v>39.6</v>
@@ -26107,23 +26122,23 @@
     </row>
     <row r="19">
       <c r="A19" s="45" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="45" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="45" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B21" s="57">
         <v>60.4</v>
@@ -26131,7 +26146,7 @@
     </row>
     <row r="22">
       <c r="A22" s="45" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B22" s="57">
         <v>39.6</v>
@@ -26139,23 +26154,23 @@
     </row>
     <row r="23">
       <c r="A23" s="45" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="45" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B25" s="60">
         <v>60.4</v>
@@ -26163,7 +26178,7 @@
     </row>
     <row r="26">
       <c r="A26" s="35" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B26" s="60">
         <v>39.6</v>
@@ -26174,19 +26189,19 @@
     </row>
     <row r="28">
       <c r="A28" s="59" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B28" s="58"/>
     </row>
     <row r="29">
       <c r="A29" s="45" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B29" s="58"/>
     </row>
     <row r="30">
       <c r="A30" s="45" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B30" s="58"/>
     </row>
@@ -35768,72 +35783,82 @@
       <c r="B35" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="C35" s="15"/>
+      <c r="C35" s="15" t="s">
+        <v>263</v>
+      </c>
       <c r="D35" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="C36" s="15"/>
+        <v>267</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>268</v>
+      </c>
       <c r="D36" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="C37" s="15"/>
+        <v>272</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>273</v>
+      </c>
       <c r="D37" s="15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="34" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="C38" s="15"/>
+        <v>277</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>278</v>
+      </c>
       <c r="D38" s="15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="34" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C39" s="15"/>
+        <v>282</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>283</v>
+      </c>
       <c r="D39" s="15" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40">
@@ -42604,13 +42629,13 @@
         <v>145</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>147</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E2" s="15"/>
     </row>
@@ -42619,13 +42644,13 @@
         <v>145</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>150</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E3" s="16"/>
     </row>
@@ -42634,13 +42659,13 @@
         <v>145</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>152</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E4" s="16"/>
     </row>
@@ -42649,13 +42674,13 @@
         <v>145</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>152</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -42664,13 +42689,13 @@
         <v>145</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>156</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E6" s="16"/>
     </row>
@@ -42679,13 +42704,13 @@
         <v>145</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>159</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E7" s="16"/>
     </row>
@@ -42694,13 +42719,13 @@
         <v>145</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>162</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E8" s="16"/>
     </row>
@@ -42709,13 +42734,13 @@
         <v>163</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>165</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E9" s="15"/>
     </row>
@@ -42724,13 +42749,13 @@
         <v>163</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>168</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -42739,13 +42764,13 @@
         <v>169</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>171</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E11" s="15"/>
     </row>
@@ -42754,13 +42779,13 @@
         <v>169</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>174</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -42769,13 +42794,13 @@
         <v>169</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E13" s="16"/>
     </row>
@@ -42784,13 +42809,13 @@
         <v>169</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>180</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E14" s="16"/>
     </row>
@@ -42799,13 +42824,13 @@
         <v>169</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>183</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E15" s="16"/>
     </row>
@@ -42814,13 +42839,13 @@
         <v>169</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>185</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="19"/>
@@ -42830,13 +42855,13 @@
         <v>169</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>177</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E17" s="16"/>
     </row>
@@ -42845,7 +42870,7 @@
         <v>188</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>190</v>
@@ -42860,13 +42885,13 @@
         <v>188</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>193</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E19" s="16"/>
     </row>
@@ -42875,7 +42900,7 @@
         <v>195</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>197</v>
@@ -42890,13 +42915,13 @@
         <v>199</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>201</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E21" s="15"/>
     </row>
@@ -42905,13 +42930,13 @@
         <v>203</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>205</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E22" s="15"/>
     </row>
@@ -42920,13 +42945,13 @@
         <v>207</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>209</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -42935,13 +42960,13 @@
         <v>211</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>213</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E24" s="15"/>
     </row>
@@ -42950,13 +42975,13 @@
         <v>215</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="26"/>
@@ -42966,13 +42991,13 @@
         <v>219</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>221</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="26"/>
@@ -42982,13 +43007,13 @@
         <v>223</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>225</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="26"/>
@@ -42998,29 +43023,29 @@
         <v>227</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>229</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="26"/>
     </row>
     <row r="29">
       <c r="A29" s="40" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>233</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="35"/>
@@ -43048,16 +43073,16 @@
     </row>
     <row r="30">
       <c r="A30" s="40" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>238</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="35"/>
@@ -43085,16 +43110,16 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>243</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35"/>
@@ -43122,16 +43147,16 @@
     </row>
     <row r="32">
       <c r="A32" s="42" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>248</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="35"/>
@@ -43159,16 +43184,16 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>253</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="35"/>
@@ -43196,16 +43221,16 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>258</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="35"/>
@@ -49069,13 +49094,13 @@
         <v>145</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E2" s="15"/>
     </row>
@@ -49084,13 +49109,13 @@
         <v>145</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E3" s="16"/>
     </row>
@@ -49099,13 +49124,13 @@
         <v>145</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E4" s="16"/>
     </row>
@@ -49114,13 +49139,13 @@
         <v>145</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -49129,13 +49154,13 @@
         <v>145</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E6" s="16"/>
     </row>
@@ -49144,13 +49169,13 @@
         <v>145</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E7" s="16"/>
     </row>
@@ -49159,13 +49184,13 @@
         <v>145</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E8" s="16"/>
     </row>
@@ -49174,13 +49199,13 @@
         <v>163</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E9" s="15"/>
     </row>
@@ -49189,13 +49214,13 @@
         <v>163</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -49204,13 +49229,13 @@
         <v>169</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E11" s="15"/>
     </row>
@@ -49219,13 +49244,13 @@
         <v>169</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -49234,13 +49259,13 @@
         <v>169</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E13" s="16"/>
     </row>
@@ -49249,13 +49274,13 @@
         <v>169</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E14" s="16"/>
     </row>
@@ -49264,13 +49289,13 @@
         <v>169</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>366</v>
-      </c>
       <c r="D15" s="31" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E15" s="16"/>
     </row>
@@ -49279,13 +49304,13 @@
         <v>169</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="19"/>
@@ -49295,13 +49320,13 @@
         <v>169</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E17" s="16"/>
     </row>
@@ -49310,13 +49335,13 @@
         <v>188</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E18" s="15"/>
     </row>
@@ -49325,13 +49350,13 @@
         <v>188</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E19" s="16"/>
     </row>
@@ -49340,10 +49365,10 @@
         <v>195</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D20" s="31" t="s">
         <v>198</v>
@@ -49355,13 +49380,13 @@
         <v>199</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E21" s="15"/>
     </row>
@@ -49370,13 +49395,13 @@
         <v>203</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E22" s="15"/>
     </row>
@@ -49385,13 +49410,13 @@
         <v>207</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -49400,13 +49425,13 @@
         <v>211</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E24" s="15"/>
     </row>
@@ -49415,13 +49440,13 @@
         <v>215</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="26"/>
@@ -49431,13 +49456,13 @@
         <v>219</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="26"/>
@@ -49447,13 +49472,13 @@
         <v>223</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="26"/>
@@ -49463,29 +49488,29 @@
         <v>227</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="26"/>
     </row>
     <row r="29">
       <c r="A29" s="40" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="35"/>
@@ -49513,16 +49538,16 @@
     </row>
     <row r="30">
       <c r="A30" s="40" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="35"/>
@@ -49550,16 +49575,16 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35"/>
@@ -49587,16 +49612,16 @@
     </row>
     <row r="32">
       <c r="A32" s="42" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="35"/>
@@ -49624,16 +49649,16 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="35"/>
@@ -49661,16 +49686,16 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="35"/>
@@ -55529,7 +55554,7 @@
         <v>145</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3">
@@ -55537,7 +55562,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4">
@@ -55545,7 +55570,7 @@
         <v>145</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5">
@@ -55553,7 +55578,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6">
@@ -55561,7 +55586,7 @@
         <v>169</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7">
@@ -55569,7 +55594,7 @@
         <v>169</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8">
@@ -55577,7 +55602,7 @@
         <v>169</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -55585,7 +55610,7 @@
         <v>188</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10">
@@ -55593,7 +55618,7 @@
         <v>195</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11">
@@ -55601,7 +55626,7 @@
         <v>199</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12">
@@ -55609,55 +55634,55 @@
         <v>203</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -55698,7 +55723,7 @@
         <v>145</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3">
@@ -55706,7 +55731,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4">
@@ -55714,7 +55739,7 @@
         <v>145</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5">
@@ -55722,7 +55747,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6">
@@ -55730,7 +55755,7 @@
         <v>169</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7">
@@ -55738,7 +55763,7 @@
         <v>169</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8">
@@ -55746,7 +55771,7 @@
         <v>169</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -55754,7 +55779,7 @@
         <v>188</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10">
@@ -55762,7 +55787,7 @@
         <v>195</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11">
@@ -55770,7 +55795,7 @@
         <v>199</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
@@ -55778,55 +55803,55 @@
         <v>203</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19">
@@ -58818,7 +58843,7 @@
         <v>145</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3">
@@ -58826,7 +58851,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4">
@@ -58834,7 +58859,7 @@
         <v>145</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5">
@@ -58842,7 +58867,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6">
@@ -58850,7 +58875,7 @@
         <v>169</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7">
@@ -58858,7 +58883,7 @@
         <v>169</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -58866,7 +58891,7 @@
         <v>169</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -58874,7 +58899,7 @@
         <v>188</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10">
@@ -58882,7 +58907,7 @@
         <v>195</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11">
@@ -58890,7 +58915,7 @@
         <v>199</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12">
@@ -58898,55 +58923,55 @@
         <v>203</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19">
@@ -61932,7 +61957,7 @@
         <v>145</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3">
@@ -61940,7 +61965,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4">
@@ -61948,7 +61973,7 @@
         <v>145</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5">
@@ -61956,7 +61981,7 @@
         <v>163</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6">
@@ -61964,7 +61989,7 @@
         <v>169</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7">
@@ -61972,7 +61997,7 @@
         <v>169</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8">
@@ -61980,7 +62005,7 @@
         <v>169</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9">
@@ -61988,7 +62013,7 @@
         <v>188</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10">
@@ -61996,7 +62021,7 @@
         <v>195</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11">
@@ -62004,7 +62029,7 @@
         <v>199</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12">
@@ -62012,55 +62037,55 @@
         <v>203</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/Texte/Textbausteine_LENA_Maerz2026.xlsx
+++ b/Texte/Textbausteine_LENA_Maerz2026.xlsx
@@ -281,7 +281,7 @@
     <t>Die Bargeldinitiative ist in #Gemeinde_d mit #JaStimmenHauptvorlageInProzent Prozent der Stimmen angenommen worden. Aber auch der Gegenvorschlag von Bundesrat und Parlament überzeugte einen Mehrheit von #JaStimmenGegenvorschlagInProzent Prozent. Bei der Stichfrage haben sich die Stimmberechtigten mit #StichentscheidZustimmungHauptvorlageInProzent Prozent für die Initiative ausgesprochen.</t>
   </si>
   <si>
-    <t>Les ayants droit de #Gemeinde_f ont tranché: ils sont favorables à l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" qui veut garantir le maintien de l'argent liquide en Suisse. Les citoyens ont dit oui à #JaStimmenHauptvorlageInProzent. Ils acceptent aussi le contre-projet du Conseil fédéral et du Parlement avec #JaStimmenGegenvorschlagInProzent % de oui. Avec cette proposition, la disponibilité de l'argent liquide est garantie par des dispositions formulées de manière juridiquement claire et applicables. Invités à choisir, les habitants de #Gemeinde_f tranchent toutefois en faveur de l'initiative avec #StichentscheidZustimmungHauptvorlageInProzent % de oui.</t>
+    <t>Les ayants droit de #Gemeinde_f ont tranché: ils sont favorables à l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" qui veut garantir le maintien de l'argent liquide en Suisse. Les citoyens ont dit oui à #JaStimmenHauptvorlageInProzent %. Ils acceptent aussi le contre-projet du Conseil fédéral et du Parlement avec #JaStimmenGegenvorschlagInProzent % de oui. Avec cette proposition, la disponibilité de l'argent liquide est garantie par des dispositions formulées de manière juridiquement claire et applicables. Invités à choisir, les habitants de #Gemeinde_f tranchent toutefois en faveur de l'initiative avec #StichentscheidZustimmungHauptvorlageInProzent % de oui.</t>
   </si>
   <si>
     <t>Sì col #JaStimmenHauptvorlageInProzent % all'Iniziativa sul denaro contante. Approvato con il #JaStimmenGegenvorschlagInProzent % anche il controprogetto. I cittadini di #Gemeinde_i hanno però preferito l'inizaitiva con il #StichentscheidZustimmungHauptvorlageInProzent % .</t>
@@ -296,13 +296,16 @@
     <t>È stata approvata col #JaStimmenHauptvorlageInProzent % l'Iniziativa sul denaro contante. Sì con il #JaStimmenGegenvorschlagInProzent % anche al controprogetto. I cittadini di #Gemeinde_i hanno però preferito l'inizaitiva con il #StichentscheidZustimmungHauptvorlageInProzent % .</t>
   </si>
   <si>
-    <t>Les ayants droit de #Gemeinde_f ont rendu leur verdict: ils soutiennent l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets", destinée à garantir le maintien de l'argent liquide en Suisse. Le texte récolte #JaStimmenHauptvorlageInProzent. Le contre-projet du Conseil fédéral et du Parlement est également accepté avec #JaStimmenGegenvorschlagInProzent % de oui. Celui-ci prévoit des dispositions juridiquement claires pour assurer la disponibilité de l'argent liquide. Lors de la question subsidiaire, les habitants de #Gemeinde_f optent toutefois pour l'initiative avec #StichentscheidZustimmungHauptvorlageInProzent % de oui.</t>
+    <t>Les ayants droit de #Gemeinde_f ont rendu leur verdict: ils soutiennent l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets", destinée à garantir le maintien de l'argent liquide en Suisse. Le texte récolte #JaStimmenHauptvorlageInProzent %. Le contre-projet du Conseil fédéral et du Parlement est également accepté avec #JaStimmenGegenvorschlagInProzent % de oui. Celui-ci prévoit des dispositions juridiquement claires pour assurer la disponibilité de l'argent liquide. Lors de la question subsidiaire, les habitants de #Gemeinde_f optent toutefois pour l'initiative avec #StichentscheidZustimmungHauptvorlageInProzent % de oui.</t>
+  </si>
+  <si>
+    <t>Sì col #JaStimmenHauptvorlageInProzent % all'Iniziativa sul denaro contante. Sì con il #JaStimmenGegenvorschlagInProzent % anche al controprogetto. I cittadini di #Gemeinde_i hanno però preferito l'iniziativa con il #StichentscheidZustimmungHauptvorlageInProzent % .</t>
   </si>
   <si>
     <t>Die Stimmberechtigten in #Gemeinde_d haben die Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent angenommen und befürworten auch den Gegenvorschlag des Bundesrat und Parlaments mit #JaStimmenGegenvorschlagInProzent Prozent. Bei der Stichfrage gaben sie mit #StichentscheidZustimmungHauptvorlageInProzent Prozent der Initiative den Vorzug.</t>
   </si>
   <si>
-    <t>À #Gemeinde_f, les électeurs soutiennent l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets", qui vise à inscrire la garantie de l'argent liquide dans le droit. Elle obtient #JaStimmenHauptvorlageInProzent. Le contre-projet du Conseil fédéral et du Parlement passe lui aussi la rampe avec #JaStimmenGegenvorschlagInProzent % de oui et entend garantir la disponibilité du numéraire par des bases légales précises. Mais à la question décisive, la majorité (#StichentscheidZustimmungHauptvorlageInProzent % de oui) choisit l'initiative.</t>
+    <t>À #Gemeinde_f, les électeurs soutiennent l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets", qui vise à inscrire la garantie de l'argent liquide dans le droit. Elle obtient #JaStimmenHauptvorlageInProzent %. Le contre-projet du Conseil fédéral et du Parlement passe lui aussi la rampe avec #JaStimmenGegenvorschlagInProzent % de oui et entend garantir la disponibilité du numéraire par des bases légales précises. Mais à la question décisive, la majorité (#StichentscheidZustimmungHauptvorlageInProzent % de oui) choisit l'initiative.</t>
   </si>
   <si>
     <t>Intro_HauptvorlageJa_GegenvorschlagJa_StichentscheidGegenvorschlag</t>
@@ -335,7 +338,7 @@
     <t>È stata approvata col #JaStimmenHauptvorlageInProzent % l'Iniziativa sul denaro contante. Sì con il #JaStimmenGegenvorschlagInProzent % anche al controprogetto. I cittadini di #Gemeinde_i hanno però preferito il controprogetto con il #StichentscheidZustimmungHauptvorlageInProzent % .</t>
   </si>
   <si>
-    <t>Die Stimmberechtigten in #Gemeinde_d haben die Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent an angenommen und befürworten auch den Gegenvorschlag von Bundesrat und Parlament mit #JaStimmenGegenvorschlagInProzent Prozent. Das Resultat der Stichfrage ergab mit #StichentscheidZustimmungGegenvorschlagInProzent Prozent den Vorzug für den Gegenvorschlag.</t>
+    <t>Die Stimmberechtigten in #Gemeinde_d haben die Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent angenommen und befürworten auch den Gegenvorschlag von Bundesrat und Parlament mit #JaStimmenGegenvorschlagInProzent Prozent. Das Resultat der Stichfrage ergab mit #StichentscheidZustimmungGegenvorschlagInProzent Prozent den Vorzug für den Gegenvorschlag.</t>
   </si>
   <si>
     <t>Les citoyens de #Gemeinde_f privilégient le contre-projet du Conseil fédéral et du Parlement, qui vise à garantir la disponibilité de l'argent liquide (#StichentscheidZustimmungGegenvorschlagInProzent % de oui à la question subsidiaire). Le texte recueille #JaStimmenGegenvorschlagInProzent % de oui. L'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" est toutefois également acceptée avec #JaStimmenHauptvorlageInProzent % de oui.</t>
@@ -362,7 +365,7 @@
     <t>Die Gemeinde #Gemeinde_d hat die Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent angenommen. Der Gegenvorschlag von Bundesrat und Parlament hingegen wurde mit #NeinStimmenGegenvorschlagInProzent Prozent abgelehnt.</t>
   </si>
   <si>
-    <t>C'est oui à #Gemeinde_f à #JaStimmenHauptvorlageInProzent % à l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets". C'est non par contre à #JaStimmenGegenvorschlagInProzent % au contre-projet du Conseil fédéral et du Parlement garantissant la disponibilité de l'argent liquide.</t>
+    <t>C'est oui à #Gemeinde_f à #JaStimmenHauptvorlageInProzent % à l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets". C'est non par contre à #NeinStimmenGegenvorschlagInProzent % au contre-projet du Conseil fédéral et du Parlement garantissant la disponibilité de l'argent liquide.</t>
   </si>
   <si>
     <t>I cittadini di #Gemeinde_i hanno approvato con il #JaStimmenHauptvorlageInProzent percento l'Initiativa sul denaro contante e si sono opposti al controprogetto con il #NeinStimmenGegenvorschlagInProzent %.</t>
@@ -371,13 +374,13 @@
     <t>#Gemeinde_d hat mit #JaStimmenHauptvorlageInProzent Prozent Ja gesagt zur Bargeldinitiative. Den Gegenvorschlag von Bundesrat und Parlament lehnte eine Mehrheit von #NeinStimmenGegenvorschlagInProzent Prozent ab.</t>
   </si>
   <si>
-    <t>À #Gemeinde_f, l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" est acceptée avec #JaStimmenHauptvorlageInProzent % de oui. Le contre-projet du Conseil fédéral et du Parlement, qui veut garantir la disponibilité de l'argent liquide, est en revanche rejeté avec #JaStimmenGegenvorschlagInProzent %.</t>
+    <t>À #Gemeinde_f, l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" est acceptée avec #JaStimmenHauptvorlageInProzent % de oui. Le contre-projet du Conseil fédéral et du Parlement, qui veut garantir la disponibilité de l'argent liquide, est en revanche rejeté avec #NeinStimmenGegenvorschlagInProzent %.</t>
   </si>
   <si>
     <t>Die Bargeldinitiative hat in #Gemeinde_d mit #JaStimmenHauptvorlageInProzent Prozent Zustimmung gefunden. Der Gegenvorschlag von Bundesrat und Parlament wurde mit #NeinStimmenGegenvorschlagInProzent Prozent mehrheitlich abgelehnt.</t>
   </si>
   <si>
-    <t>Les électeurs de #Gemeinde_f approuvent à #JaStimmenHauptvorlageInProzent % l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets". Ils refusent en revanche le contre-projet du Conseil fédéral et du Parlement garantissant la disponibilité de l'argent liquide (#JaStimmenGegenvorschlagInProzent %).</t>
+    <t>Les électeurs de #Gemeinde_f approuvent à #JaStimmenHauptvorlageInProzent % l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets". Ils refusent en revanche le contre-projet du Conseil fédéral et du Parlement garantissant la disponibilité de l'argent liquide (#NeinStimmenGegenvorschlagInProzent %).</t>
   </si>
   <si>
     <t>In #Gemeinde_d hat die Stimmbevölkerung der Bargeldinitiative mit #JaStimmenHauptvorlageInProzent Prozent zugestimmt. Eine Mehrheit von #NeinStimmenGegenvorschlagInProzent Prozent lehnte den Gegenvorschlag von Bundesrat und Parlament ab.</t>
@@ -797,7 +800,7 @@
     <t>HistoricPhrase_Nein_Nein_NeinAnteilGesunken</t>
   </si>
   <si>
-    <t>Damit hat die Ablehung in #Gemeinde_d im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 abgenommen. Damals betrug der Nein-Stimmen-Anteil noch #HistNeinStimmenInProzent Prozent.</t>
+    <t>Damit hat die Ablehnung in #Gemeinde_d im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 abgenommen. Damals betrug der Nein-Stimmen-Anteil noch #HistNeinStimmenInProzent Prozent.</t>
   </si>
   <si>
     <t>#Gemeinde_f et le canton #Kanton_f rejettent l'initiative populaire pour réduire la redevance radio-TV à 200 francs par an.</t>
@@ -812,7 +815,7 @@
     <t>HistoricPhrase_Nein_Nein_NeinAnteilÄhnlich</t>
   </si>
   <si>
-    <t>Damit ist in #Gemeinde_d die Ablehnung im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 ungefähr gleich geblieten.</t>
+    <t>Damit ist in #Gemeinde_d die Ablehnung im Vergleich zur Abstimmung über die No-Billag-Initiative im Jahr 2018 ungefähr gleich geblieben.</t>
   </si>
   <si>
     <t>Le rejet de l'initiative dimanche à #Gemeinde_f est proche à celui de l'initiative No Billag en 2018.</t>
@@ -1169,9 +1172,6 @@
     <t>A #Gemeinde_i l'iniziativa sull'imposizione individuale è respinta con il #NeinStimmenInProzent per cento.</t>
   </si>
   <si>
-    <t>A #Gemeinde_i l'iniziativa sull'imposizione individuale è respinto con il #NeinStimmenInProzent per cento.</t>
-  </si>
-  <si>
     <t>#NeinStimmenInProzent Prozent der Stimmbürgerinnen und Stimmbürger von #Gemeinde_d haben die Individualbesteuerung abgelehnt.</t>
   </si>
   <si>
@@ -1253,7 +1253,7 @@
     <t>#Gemeinde_d verzeichnet den höchsten Nein-Anteil in der Schweiz zur Individualbesteuerung mit #NeinStimmenInProzent Prozent.</t>
   </si>
   <si>
-    <t>Taux de non maximal en Suisse pour Loi sur l'e-ID à #Gemeinde_f : #NeinStimmenInProzent pour cent.</t>
+    <t>C'est à #Gemeinde_f qu'a été enregistré le plus fort taux de non à l'imposition individuelle des couples mariés avec #NeinStimmenInProzent pour cent.</t>
   </si>
   <si>
     <t>Per l'iniziativa sull'imposizione individuale, #Gemeinde_i tocca il massimo nazionale di no con il #NeinStimmenInProzent per cento.</t>
@@ -7955,7 +7955,7 @@
     </row>
     <row r="2">
       <c r="A2" s="49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="26" t="s">
@@ -7964,7 +7964,7 @@
     </row>
     <row r="3">
       <c r="A3" s="49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="50"/>
       <c r="C3" s="26" t="s">
@@ -7973,7 +7973,7 @@
     </row>
     <row r="4">
       <c r="A4" s="49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="26" t="s">
@@ -7982,7 +7982,7 @@
     </row>
     <row r="5">
       <c r="A5" s="49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="26" t="s">
@@ -7991,7 +7991,7 @@
     </row>
     <row r="6">
       <c r="A6" s="51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="35"/>
       <c r="C6" s="26" t="s">
@@ -8000,7 +8000,7 @@
     </row>
     <row r="7">
       <c r="A7" s="51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="35"/>
       <c r="C7" s="26" t="s">
@@ -8009,7 +8009,7 @@
     </row>
     <row r="8">
       <c r="A8" s="51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="26" t="s">
@@ -8018,7 +8018,7 @@
     </row>
     <row r="9">
       <c r="A9" s="51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="35"/>
       <c r="C9" s="26" t="s">
@@ -8027,7 +8027,7 @@
     </row>
     <row r="10">
       <c r="A10" s="52" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="26" t="s">
@@ -8036,7 +8036,7 @@
     </row>
     <row r="11">
       <c r="A11" s="52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="26" t="s">
@@ -8045,7 +8045,7 @@
     </row>
     <row r="12">
       <c r="A12" s="52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="35"/>
       <c r="C12" s="26" t="s">
@@ -8054,7 +8054,7 @@
     </row>
     <row r="13">
       <c r="A13" s="40" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="35"/>
       <c r="C13" s="26" t="s">
@@ -8063,7 +8063,7 @@
     </row>
     <row r="14">
       <c r="A14" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="35"/>
       <c r="C14" s="26" t="s">
@@ -8072,7 +8072,7 @@
     </row>
     <row r="15">
       <c r="A15" s="42" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="35"/>
       <c r="C15" s="26" t="s">
@@ -8081,7 +8081,7 @@
     </row>
     <row r="16">
       <c r="A16" s="42" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="35"/>
       <c r="C16" s="26" t="s">
@@ -8090,7 +8090,7 @@
     </row>
     <row r="17">
       <c r="A17" s="42" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="35"/>
       <c r="C17" s="26" t="s">
@@ -8099,7 +8099,7 @@
     </row>
     <row r="18">
       <c r="A18" s="42" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="26" t="s">
@@ -8144,7 +8144,7 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -8162,7 +8162,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8171,7 +8171,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -8180,7 +8180,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -8189,7 +8189,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -8207,7 +8207,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -8216,7 +8216,7 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="19"/>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -8243,7 +8243,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -8252,7 +8252,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -8261,7 +8261,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -8288,7 +8288,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -14131,7 +14131,7 @@
     </row>
     <row r="5">
       <c r="A5" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="54"/>
@@ -14140,7 +14140,7 @@
     </row>
     <row r="6">
       <c r="A6" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="54"/>
@@ -14149,7 +14149,7 @@
     </row>
     <row r="7">
       <c r="A7" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="54"/>
@@ -14158,7 +14158,7 @@
     </row>
     <row r="8">
       <c r="A8" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="54"/>
@@ -14167,7 +14167,7 @@
     </row>
     <row r="9">
       <c r="A9" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="54"/>
@@ -14176,7 +14176,7 @@
     </row>
     <row r="10">
       <c r="A10" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="54"/>
@@ -14185,7 +14185,7 @@
     </row>
     <row r="11">
       <c r="A11" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="54"/>
@@ -14194,7 +14194,7 @@
     </row>
     <row r="12">
       <c r="A12" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="54"/>
@@ -14203,7 +14203,7 @@
     </row>
     <row r="13">
       <c r="A13" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="54"/>
@@ -14212,7 +14212,7 @@
     </row>
     <row r="14">
       <c r="A14" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="54"/>
@@ -14221,7 +14221,7 @@
     </row>
     <row r="15">
       <c r="A15" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="54"/>
@@ -14230,7 +14230,7 @@
     </row>
     <row r="16">
       <c r="A16" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="54"/>
@@ -20046,7 +20046,7 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -20055,7 +20055,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -20064,7 +20064,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -20073,7 +20073,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -20082,7 +20082,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -20091,7 +20091,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -20100,7 +20100,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -20109,7 +20109,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -20118,7 +20118,7 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="19"/>
@@ -20127,7 +20127,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -20136,7 +20136,7 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -20145,7 +20145,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -20154,7 +20154,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -20163,7 +20163,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -20172,7 +20172,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -20181,7 +20181,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -20190,7 +20190,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -29202,7 +29202,7 @@
         <v>90</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -29211,10 +29211,10 @@
         <v>80</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>83</v>
@@ -29223,301 +29223,301 @@
     </row>
     <row r="7">
       <c r="A7" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="16"/>
     </row>
     <row r="8">
       <c r="A8" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" s="16"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" s="16"/>
     </row>
     <row r="10">
       <c r="A10" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="16"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="16"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E12" s="16"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" s="16"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E14" s="16"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" s="16"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>117</v>
-      </c>
       <c r="D16" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E18" s="16"/>
     </row>
     <row r="19">
       <c r="A19" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E19" s="16"/>
     </row>
     <row r="20">
       <c r="A20" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E20" s="16"/>
     </row>
     <row r="21">
       <c r="A21" s="24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E21" s="16"/>
     </row>
     <row r="22">
       <c r="A22" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E22" s="16"/>
     </row>
     <row r="23">
       <c r="A23" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E23" s="16"/>
     </row>
     <row r="24">
       <c r="A24" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" s="16"/>
     </row>
@@ -35266,599 +35266,599 @@
     </row>
     <row r="2">
       <c r="A2" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E2" s="31"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>148</v>
       </c>
       <c r="E3" s="26"/>
     </row>
     <row r="4">
       <c r="A4" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E4" s="26"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>154</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>153</v>
       </c>
       <c r="E5" s="26"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E6" s="26"/>
     </row>
     <row r="7">
       <c r="A7" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E7" s="26"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E8" s="26"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E9" s="31"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B10" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>167</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>166</v>
       </c>
       <c r="E10" s="26"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E11" s="31"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E12" s="26"/>
     </row>
     <row r="13">
       <c r="A13" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E13" s="26"/>
     </row>
     <row r="14">
       <c r="A14" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E14" s="26"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="31" t="s">
         <v>182</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>181</v>
       </c>
       <c r="E15" s="26"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="19"/>
     </row>
     <row r="17">
       <c r="A17" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" s="26"/>
     </row>
     <row r="18">
       <c r="A18" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E18" s="31"/>
     </row>
     <row r="19">
       <c r="A19" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E19" s="26"/>
     </row>
     <row r="20">
       <c r="A20" s="33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E20" s="31"/>
     </row>
     <row r="21">
       <c r="A21" s="33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E21" s="31"/>
     </row>
     <row r="22">
       <c r="A22" s="33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E22" s="31"/>
     </row>
     <row r="23">
       <c r="A23" s="24" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E23" s="31"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E24" s="31"/>
     </row>
     <row r="25">
       <c r="A25" s="24" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="26"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E26" s="31"/>
       <c r="F26" s="26"/>
     </row>
     <row r="27">
       <c r="A27" s="24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E27" s="31"/>
       <c r="F27" s="26"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="26"/>
     </row>
     <row r="29">
       <c r="A29" s="34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="34" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="40">
@@ -42626,426 +42626,426 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E2" s="15"/>
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E3" s="16"/>
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E4" s="16"/>
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E5" s="16"/>
     </row>
     <row r="6">
       <c r="A6" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E6" s="16"/>
     </row>
     <row r="7">
       <c r="A7" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E7" s="16"/>
     </row>
     <row r="8">
       <c r="A8" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E8" s="16"/>
     </row>
     <row r="9">
       <c r="A9" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E9" s="15"/>
     </row>
     <row r="10">
       <c r="A10" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B10" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>298</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>297</v>
       </c>
       <c r="E10" s="16"/>
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E11" s="15"/>
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E12" s="16"/>
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E13" s="16"/>
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>305</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="E14" s="16"/>
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E15" s="16"/>
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="19"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="31" t="s">
         <v>310</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>309</v>
       </c>
       <c r="E17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E18" s="15"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E19" s="16"/>
     </row>
     <row r="20">
       <c r="A20" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E20" s="15"/>
     </row>
     <row r="21">
       <c r="A21" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E21" s="15"/>
     </row>
     <row r="22">
       <c r="A22" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E22" s="15"/>
     </row>
     <row r="23">
       <c r="A23" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E23" s="15"/>
     </row>
     <row r="24">
       <c r="A24" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="26"/>
     </row>
     <row r="26">
       <c r="A26" s="39" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="26"/>
     </row>
     <row r="27">
       <c r="A27" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="26"/>
     </row>
     <row r="28">
       <c r="A28" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="26"/>
     </row>
     <row r="29">
       <c r="A29" s="40" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="35"/>
@@ -43073,16 +43073,16 @@
     </row>
     <row r="30">
       <c r="A30" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="35"/>
@@ -43110,16 +43110,16 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35"/>
@@ -43147,16 +43147,16 @@
     </row>
     <row r="32">
       <c r="A32" s="42" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="35"/>
@@ -43184,16 +43184,16 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="35"/>
@@ -43221,16 +43221,16 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="35"/>
@@ -49091,233 +49091,233 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E2" s="15"/>
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E3" s="16"/>
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>355</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>354</v>
       </c>
       <c r="E4" s="16"/>
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E5" s="16"/>
     </row>
     <row r="6">
       <c r="A6" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E6" s="16"/>
     </row>
     <row r="7">
       <c r="A7" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E7" s="16"/>
     </row>
     <row r="8">
       <c r="A8" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E8" s="16"/>
     </row>
     <row r="9">
       <c r="A9" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E9" s="15"/>
     </row>
     <row r="10">
       <c r="A10" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>368</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>367</v>
       </c>
       <c r="E10" s="16"/>
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E11" s="15"/>
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E12" s="16"/>
     </row>
     <row r="13">
       <c r="A13" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>375</v>
       </c>
       <c r="E13" s="16"/>
     </row>
     <row r="14">
       <c r="A14" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E14" s="16"/>
     </row>
     <row r="15">
       <c r="A15" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="D15" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="D15" s="19" t="s">
         <v>381</v>
       </c>
       <c r="E15" s="16"/>
     </row>
     <row r="16">
       <c r="A16" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>382</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="19"/>
     </row>
     <row r="17">
       <c r="A17" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>383</v>
@@ -49332,7 +49332,7 @@
     </row>
     <row r="18">
       <c r="A18" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>386</v>
@@ -49347,13 +49347,13 @@
     </row>
     <row r="19">
       <c r="A19" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>389</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>390</v>
@@ -49362,7 +49362,7 @@
     </row>
     <row r="20">
       <c r="A20" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>391</v>
@@ -49371,13 +49371,13 @@
         <v>392</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E20" s="15"/>
     </row>
     <row r="21">
       <c r="A21" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>393</v>
@@ -49392,7 +49392,7 @@
     </row>
     <row r="22">
       <c r="A22" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>396</v>
@@ -49407,7 +49407,7 @@
     </row>
     <row r="23">
       <c r="A23" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>399</v>
@@ -49422,7 +49422,7 @@
     </row>
     <row r="24">
       <c r="A24" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>402</v>
@@ -49437,7 +49437,7 @@
     </row>
     <row r="25">
       <c r="A25" s="39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>405</v>
@@ -49453,7 +49453,7 @@
     </row>
     <row r="26">
       <c r="A26" s="39" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>408</v>
@@ -49469,7 +49469,7 @@
     </row>
     <row r="27">
       <c r="A27" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>411</v>
@@ -49485,7 +49485,7 @@
     </row>
     <row r="28">
       <c r="A28" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>414</v>
@@ -49501,7 +49501,7 @@
     </row>
     <row r="29">
       <c r="A29" s="40" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>417</v>
@@ -49538,7 +49538,7 @@
     </row>
     <row r="30">
       <c r="A30" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>420</v>
@@ -49575,7 +49575,7 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>423</v>
@@ -49612,7 +49612,7 @@
     </row>
     <row r="32">
       <c r="A32" s="42" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>426</v>
@@ -49649,7 +49649,7 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>429</v>
@@ -49686,7 +49686,7 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>432</v>
@@ -55551,7 +55551,7 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="35" t="s">
         <v>435</v>
@@ -55559,7 +55559,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="35" t="s">
         <v>436</v>
@@ -55567,7 +55567,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>437</v>
@@ -55575,7 +55575,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="35" t="s">
         <v>438</v>
@@ -55583,7 +55583,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>439</v>
@@ -55591,7 +55591,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="35" t="s">
         <v>440</v>
@@ -55599,7 +55599,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>441</v>
@@ -55607,7 +55607,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>442</v>
@@ -55615,7 +55615,7 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>443</v>
@@ -55623,7 +55623,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="35" t="s">
         <v>444</v>
@@ -55631,7 +55631,7 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="35" t="s">
         <v>445</v>
@@ -55639,7 +55639,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="35" t="s">
         <v>446</v>
@@ -55647,7 +55647,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>447</v>
@@ -55655,7 +55655,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="35" t="s">
         <v>448</v>
@@ -55663,7 +55663,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>449</v>
@@ -55671,7 +55671,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="35" t="s">
         <v>450</v>
@@ -55679,7 +55679,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>451</v>
@@ -55720,7 +55720,7 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>452</v>
@@ -55728,7 +55728,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>453</v>
@@ -55736,7 +55736,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="43" t="s">
         <v>454</v>
@@ -55744,7 +55744,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>455</v>
@@ -55752,7 +55752,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="43" t="s">
         <v>456</v>
@@ -55760,7 +55760,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="43" t="s">
         <v>457</v>
@@ -55768,7 +55768,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="43" t="s">
         <v>456</v>
@@ -55776,7 +55776,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>458</v>
@@ -55784,7 +55784,7 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="43" t="s">
         <v>459</v>
@@ -55792,7 +55792,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="43" t="s">
         <v>460</v>
@@ -55800,7 +55800,7 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="43" t="s">
         <v>461</v>
@@ -55808,7 +55808,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="43" t="s">
         <v>462</v>
@@ -55816,7 +55816,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="43" t="s">
         <v>463</v>
@@ -55824,7 +55824,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>464</v>
@@ -55832,7 +55832,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="43" t="s">
         <v>465</v>
@@ -55840,7 +55840,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="43" t="s">
         <v>466</v>
@@ -55848,7 +55848,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="43" t="s">
         <v>467</v>
@@ -58840,7 +58840,7 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>468</v>
@@ -58848,7 +58848,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>469</v>
@@ -58856,7 +58856,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>470</v>
@@ -58864,7 +58864,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="31" t="s">
         <v>471</v>
@@ -58872,7 +58872,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>472</v>
@@ -58880,7 +58880,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>473</v>
@@ -58888,7 +58888,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>474</v>
@@ -58896,7 +58896,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>475</v>
@@ -58904,7 +58904,7 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>476</v>
@@ -58912,7 +58912,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>477</v>
@@ -58920,7 +58920,7 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>478</v>
@@ -58928,7 +58928,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>479</v>
@@ -58936,7 +58936,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>480</v>
@@ -58944,7 +58944,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>481</v>
@@ -58952,7 +58952,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>482</v>
@@ -58960,7 +58960,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>483</v>
@@ -58968,7 +58968,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>484</v>
@@ -61954,7 +61954,7 @@
     </row>
     <row r="2">
       <c r="A2" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>485</v>
@@ -61962,7 +61962,7 @@
     </row>
     <row r="3">
       <c r="A3" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>486</v>
@@ -61970,7 +61970,7 @@
     </row>
     <row r="4">
       <c r="A4" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>486</v>
@@ -61978,7 +61978,7 @@
     </row>
     <row r="5">
       <c r="A5" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>487</v>
@@ -61986,7 +61986,7 @@
     </row>
     <row r="6">
       <c r="A6" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>488</v>
@@ -61994,7 +61994,7 @@
     </row>
     <row r="7">
       <c r="A7" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>489</v>
@@ -62002,7 +62002,7 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>490</v>
@@ -62010,7 +62010,7 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>491</v>
@@ -62018,7 +62018,7 @@
     </row>
     <row r="10">
       <c r="A10" s="38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>492</v>
@@ -62026,7 +62026,7 @@
     </row>
     <row r="11">
       <c r="A11" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>493</v>
@@ -62034,7 +62034,7 @@
     </row>
     <row r="12">
       <c r="A12" s="38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>494</v>
@@ -62042,7 +62042,7 @@
     </row>
     <row r="13">
       <c r="A13" s="46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>495</v>
@@ -62050,7 +62050,7 @@
     </row>
     <row r="14">
       <c r="A14" s="46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>496</v>
@@ -62058,7 +62058,7 @@
     </row>
     <row r="15">
       <c r="A15" s="47" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>497</v>
@@ -62066,7 +62066,7 @@
     </row>
     <row r="16">
       <c r="A16" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>498</v>
@@ -62074,7 +62074,7 @@
     </row>
     <row r="17">
       <c r="A17" s="47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>499</v>
@@ -62082,7 +62082,7 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>500</v>

--- a/Texte/Textbausteine_LENA_Maerz2026.xlsx
+++ b/Texte/Textbausteine_LENA_Maerz2026.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="553">
   <si>
     <t>Kanton</t>
   </si>
@@ -356,7 +356,7 @@
     <t>Die Bargeldinitiative ist in #Gemeinde_d mit #JaStimmenHauptvorlageInProzent Prozent der Stimmen angenommen worden. Der Gegenvorschlag von Bundesrat und Parlament hingegen wurde mit #NeinStimmenGegenvorschlagInProzent Prozent abgelehnt.</t>
   </si>
   <si>
-    <t>Les citoyens de #Gemeinde_f disent oui à #JaStimmenHauptvorlageInProzent à l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets". Ils s'opposent par contre au contre-projet du Conseil fédéral et du Parlement avec #NeinStimmenGegenvorschlagInProzent % de non.</t>
+    <t>Les citoyens de #Gemeinde_f disent oui à #JaStimmenHauptvorlageInProzent % à l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets". Ils s'opposent par contre au contre-projet du Conseil fédéral et du Parlement avec #NeinStimmenGegenvorschlagInProzent % de non.</t>
   </si>
   <si>
     <t>I cittadini di #Gemeinde_i hanno detto sì con il #JaStimmenHauptvorlageInProzent percento all'Initiativa sul denaro contante e si sono opposti al controprogetto con il #NeinStimmenGegenvorschlagInProzent %.</t>
@@ -401,7 +401,7 @@
     <t>#Gemeinde_d hat sich mit #NeinStimmenHauptvorlageInProzent Prozent gegen die Bargeldinitiative ausgesprochen. Der Gegenvorschlag des Bundesrat und Parlamentes hingegen wurde mit #JaStimmenGegenvorschlagInProzent Prozent angenommen.</t>
   </si>
   <si>
-    <t>Les citoyens de #Gemeinde_f disent oui à #JaStimmenGegenvorschlagInProzent à un contre-projet du Conseil fédéral et du Parlement garantissant la disponibilité de l'argent liquide. Ils refusent par contre l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" (non à #NeinStimmenHauptvorlageInProzent %).</t>
+    <t>Les citoyens de #Gemeinde_f disent oui à #JaStimmenGegenvorschlagInProzent % à un contre-projet du Conseil fédéral et du Parlement garantissant la disponibilité de l'argent liquide. Ils refusent par contre l'initiative "Oui à une monnaie suisse libre et indépendante sous forme de pièces ou de billets" (non à #NeinStimmenHauptvorlageInProzent %).</t>
   </si>
   <si>
     <t>I cittadini di #Gemeinde_i hanno bocciato con il #JaStimmenGegenvorschlagInProzent % il controprogetto all'Iniziativa sul denaro contante, mentre hanno bociato il testo principale (no al #NeinStimmenHauptvorlageInProzent %).</t>
@@ -1079,7 +1079,7 @@
     <t>In #Gemeinde_d wird die Individualbesteuerung mit #JaStimmenInProzent Prozent angenommen.</t>
   </si>
   <si>
-    <t>La population de #Gemeinde_f  approuve à #JaStimmenInProzent pour cent l'imposition individuelle des couples mariés.</t>
+    <t>La population de #Gemeinde_f approuve à #JaStimmenInProzent pour cent l'imposition individuelle des couples mariés.</t>
   </si>
   <si>
     <t>Sì all'iniziativa sull'imposizione individuale a #Gemeinde_i: #JaStimmenInProzent per cento.</t>
@@ -1088,7 +1088,7 @@
     <t>#Gemeinde_d hat die Individualbesteuerung angenommen, und der Ja-Stimmen-Anteil liegt bei #JaStimmenInProzent Prozent.</t>
   </si>
   <si>
-    <t>l'imposition individuelle des couples mariés est acceptée à #Gemeinde_f par #JaStimmenInProzent pour cent des suffrages.</t>
+    <t>L'imposition individuelle des couples mariés est acceptée à #Gemeinde_f par #JaStimmenInProzent pour cent des suffrages.</t>
   </si>
   <si>
     <t>La popolazione di #Gemeinde_i approva con il #JaStimmenInProzent per cento l'iniziativa sull'imposizione individuale.</t>
@@ -1100,22 +1100,19 @@
     <t>In #Gemeinde_d erhält die Individualbesteuerung #JaStimmenInProzent Prozent Zustimmung.</t>
   </si>
   <si>
-    <t>L'imposition individuelle des couples mariés est acceptée à #Gemeinde_f par #JaStimmenInProzent pour cent des suffrages.</t>
-  </si>
-  <si>
     <t>Con il #JaStimmenInProzent per cento dei voti, #Gemeinde_i approva l'iniziativa sull'imposizione individuale.</t>
   </si>
   <si>
     <t>#JaStimmenInProzent Prozent der Stimmbürgerinnen und Stimmbürger von #Gemeinde_d haben sich für die Individualbesteuerung ausgesprochen.</t>
   </si>
   <si>
-    <t>La population de #Gemeinde_f  accepte à #JaStimmenInProzent pour cent l'imposition individuelle des couples mariés.</t>
+    <t>La population de #Gemeinde_f accepte à #JaStimmenInProzent pour cent l'imposition individuelle des couples mariés.</t>
   </si>
   <si>
     <t>La popolazione di #Gemeinde_i approva l'iniziativa sull'imposizione individuale con il #JaStimmenInProzent per cento.</t>
   </si>
   <si>
-    <t>l'imposition individuelle des couples mariés recueille #JaStimmenInProzent pour cent % de oui à #Gemeinde_f.</t>
+    <t>L'imposition individuelle des couples mariés recueille #JaStimmenInProzent pour cent % de oui à #Gemeinde_f.</t>
   </si>
   <si>
     <t>L'iniziativa sull'imposizione individuale ottiene il #JaStimmenInProzent per cento di consensi a #Gemeinde_i.</t>
@@ -1235,7 +1232,7 @@
     <t>Schweizweit findet sich in #Gemeinde_d der zweithöchste Ja-Anteil zur Individualbesteuerung mit #JaStimmenInProzent Prozent.</t>
   </si>
   <si>
-    <t>Sur l'imposition individuelle des couples mariés, #Gemeinde_f se classe au deuxième rang en Suisse avec #JaStimmenInProzent pour cent % de votes favorables.</t>
+    <t>Sur l'imposition individuelle des couples mariés, #Gemeinde_f se classe au deuxième rang en Suisse avec #JaStimmenInProzent pour cent de votes favorables.</t>
   </si>
   <si>
     <t>#Gemeinde_i ottiene il secondo più alto tasso di sì in Svizzera per l'iniziativa sull'imposizione individuale con il #JaStimmenInProzent per cento.</t>
@@ -1262,7 +1259,7 @@
     <t>Schweizweit Rang zwei beim Nein-Anteil zu Abschafffung des Eigenmietwerts für #Gemeinde_d: #NeinStimmenInProzent Prozent.</t>
   </si>
   <si>
-    <t>#Gemeinde_f affiche le deuxième taux de non de Suisse pour Loi sur l'e-ID : #NeinStimmenInProzent pour cent.</t>
+    <t>#Gemeinde_f affiche le deuxième taux de non de Suisse pour l'imposition individuelle : #NeinStimmenInProzent pour cent.</t>
   </si>
   <si>
     <t>Per l'iniziativa sull'imposizione individuale, #Gemeinde_i si colloca al secondo posto nazionale per il no con il #NeinStimmenInProzent per cento.</t>
@@ -1271,7 +1268,7 @@
     <t>#Gemeinde_d erreicht den dritthöchsten Nein-Anteil der Schweiz zu Abschafffung des Eigenmietwerts: #NeinStimmenInProzent Prozent.</t>
   </si>
   <si>
-    <t>À l’échelle suisse, #Gemeinde_f obtient le troisième meilleur taux de non à Loi sur l'e-ID : #NeinStimmenInProzent pour cent.</t>
+    <t>À l’échelle suisse, #Gemeinde_f obtient le troisième meilleur taux de non à l'imposition individuelle : #NeinStimmenInProzent pour cent.</t>
   </si>
   <si>
     <t>#Gemeinde_i registra il terzo più alto tasso di no in Svizzera per l'iniziativa sull'imposizione individuale con il #NeinStimmenInProzent per cento.</t>
@@ -7959,7 +7956,7 @@
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -7968,7 +7965,7 @@
       </c>
       <c r="B3" s="50"/>
       <c r="C3" s="26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4">
@@ -7977,7 +7974,7 @@
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="26" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5">
@@ -7986,7 +7983,7 @@
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6">
@@ -7995,7 +7992,7 @@
       </c>
       <c r="B6" s="35"/>
       <c r="C6" s="26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7">
@@ -8004,7 +8001,7 @@
       </c>
       <c r="B7" s="35"/>
       <c r="C7" s="26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -8013,7 +8010,7 @@
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="26" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
@@ -8022,7 +8019,7 @@
       </c>
       <c r="B9" s="35"/>
       <c r="C9" s="26" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10">
@@ -8031,7 +8028,7 @@
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="26" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11">
@@ -8040,7 +8037,7 @@
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12">
@@ -8049,7 +8046,7 @@
       </c>
       <c r="B12" s="35"/>
       <c r="C12" s="26" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13">
@@ -8058,7 +8055,7 @@
       </c>
       <c r="B13" s="35"/>
       <c r="C13" s="26" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14">
@@ -8067,7 +8064,7 @@
       </c>
       <c r="B14" s="35"/>
       <c r="C14" s="26" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15">
@@ -8076,7 +8073,7 @@
       </c>
       <c r="B15" s="35"/>
       <c r="C15" s="26" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16">
@@ -8085,7 +8082,7 @@
       </c>
       <c r="B16" s="35"/>
       <c r="C16" s="26" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17">
@@ -8094,7 +8091,7 @@
       </c>
       <c r="B17" s="35"/>
       <c r="C17" s="26" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18">
@@ -8103,7 +8100,7 @@
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="26" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -25985,47 +25982,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="55" t="s">
+        <v>517</v>
+      </c>
+      <c r="B1" s="56" t="s">
         <v>518</v>
-      </c>
-      <c r="B1" s="56" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" s="57" t="s">
         <v>520</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="45" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" s="57" t="s">
         <v>522</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" s="57" t="s">
         <v>524</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="45" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" s="57" t="s">
         <v>526</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="45" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B6" s="57">
         <v>60.4</v>
@@ -26033,7 +26030,7 @@
     </row>
     <row r="7">
       <c r="A7" s="45" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B7" s="57">
         <v>39.6</v>
@@ -26041,23 +26038,23 @@
     </row>
     <row r="8">
       <c r="A8" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8" s="57" t="s">
         <v>530</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="45" t="s">
+        <v>531</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>532</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="45" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B10" s="57">
         <v>60.4</v>
@@ -26065,7 +26062,7 @@
     </row>
     <row r="11">
       <c r="A11" s="45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B11" s="57">
         <v>39.6</v>
@@ -26073,26 +26070,26 @@
     </row>
     <row r="12">
       <c r="A12" s="45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="45" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="45" t="s">
+        <v>537</v>
+      </c>
+      <c r="B14" s="57" t="s">
         <v>538</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="15">
@@ -26100,13 +26097,13 @@
     </row>
     <row r="16">
       <c r="A16" s="59" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B16" s="58"/>
     </row>
     <row r="17">
       <c r="A17" s="45" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B17" s="57">
         <v>60.4</v>
@@ -26114,7 +26111,7 @@
     </row>
     <row r="18">
       <c r="A18" s="45" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B18" s="57">
         <v>39.6</v>
@@ -26122,23 +26119,23 @@
     </row>
     <row r="19">
       <c r="A19" s="45" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B19" s="57" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="45" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="45" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B21" s="57">
         <v>60.4</v>
@@ -26146,7 +26143,7 @@
     </row>
     <row r="22">
       <c r="A22" s="45" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B22" s="57">
         <v>39.6</v>
@@ -26154,23 +26151,23 @@
     </row>
     <row r="23">
       <c r="A23" s="45" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B23" s="57" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="45" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B25" s="60">
         <v>60.4</v>
@@ -26178,7 +26175,7 @@
     </row>
     <row r="26">
       <c r="A26" s="35" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B26" s="60">
         <v>39.6</v>
@@ -26189,19 +26186,19 @@
     </row>
     <row r="28">
       <c r="A28" s="59" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B28" s="58"/>
     </row>
     <row r="29">
       <c r="A29" s="45" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B29" s="58"/>
     </row>
     <row r="30">
       <c r="A30" s="45" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B30" s="58"/>
     </row>
@@ -49142,10 +49139,10 @@
         <v>357</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>358</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>359</v>
       </c>
       <c r="E5" s="16"/>
     </row>
@@ -49154,13 +49151,13 @@
         <v>146</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="19" t="s">
         <v>361</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>362</v>
       </c>
       <c r="E6" s="16"/>
     </row>
@@ -49169,13 +49166,13 @@
         <v>146</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C7" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>363</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>364</v>
       </c>
       <c r="E7" s="16"/>
     </row>
@@ -49187,10 +49184,10 @@
         <v>357</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E8" s="16"/>
     </row>
@@ -49199,13 +49196,13 @@
         <v>164</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>366</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="31" t="s">
         <v>367</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>368</v>
       </c>
       <c r="E9" s="15"/>
     </row>
@@ -49214,13 +49211,13 @@
         <v>164</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>370</v>
-      </c>
       <c r="D10" s="31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -49229,13 +49226,13 @@
         <v>170</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="31" t="s">
         <v>372</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>373</v>
       </c>
       <c r="E11" s="15"/>
     </row>
@@ -49244,13 +49241,13 @@
         <v>170</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="D12" s="19" t="s">
         <v>375</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>376</v>
       </c>
       <c r="E12" s="16"/>
     </row>
@@ -49259,13 +49256,13 @@
         <v>170</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>378</v>
-      </c>
       <c r="D13" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E13" s="16"/>
     </row>
@@ -49274,13 +49271,13 @@
         <v>170</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
         <v>380</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>381</v>
       </c>
       <c r="E14" s="16"/>
     </row>
@@ -49289,13 +49286,13 @@
         <v>170</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E15" s="16"/>
     </row>
@@ -49304,13 +49301,13 @@
         <v>170</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="19"/>
@@ -49320,13 +49317,13 @@
         <v>170</v>
       </c>
       <c r="B17" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="D17" s="19" t="s">
         <v>384</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>385</v>
       </c>
       <c r="E17" s="16"/>
     </row>
@@ -49335,13 +49332,13 @@
         <v>189</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>387</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>388</v>
       </c>
       <c r="E18" s="15"/>
     </row>
@@ -49350,13 +49347,13 @@
         <v>189</v>
       </c>
       <c r="B19" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>389</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>380</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>390</v>
       </c>
       <c r="E19" s="16"/>
     </row>
@@ -49365,10 +49362,10 @@
         <v>196</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>391</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>392</v>
       </c>
       <c r="D20" s="31" t="s">
         <v>199</v>
@@ -49380,13 +49377,13 @@
         <v>200</v>
       </c>
       <c r="B21" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="31" t="s">
         <v>394</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>395</v>
       </c>
       <c r="E21" s="15"/>
     </row>
@@ -49395,13 +49392,13 @@
         <v>204</v>
       </c>
       <c r="B22" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="D22" s="31" t="s">
         <v>397</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>398</v>
       </c>
       <c r="E22" s="15"/>
     </row>
@@ -49410,13 +49407,13 @@
         <v>208</v>
       </c>
       <c r="B23" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="D23" s="31" t="s">
         <v>400</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>401</v>
       </c>
       <c r="E23" s="15"/>
     </row>
@@ -49425,13 +49422,13 @@
         <v>212</v>
       </c>
       <c r="B24" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="31" t="s">
         <v>403</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>404</v>
       </c>
       <c r="E24" s="15"/>
     </row>
@@ -49440,13 +49437,13 @@
         <v>216</v>
       </c>
       <c r="B25" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="D25" s="31" t="s">
         <v>406</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>407</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="26"/>
@@ -49456,13 +49453,13 @@
         <v>220</v>
       </c>
       <c r="B26" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="D26" s="31" t="s">
         <v>409</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>410</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="26"/>
@@ -49472,13 +49469,13 @@
         <v>224</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="D27" s="31" t="s">
         <v>412</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>413</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="26"/>
@@ -49488,13 +49485,13 @@
         <v>228</v>
       </c>
       <c r="B28" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="D28" s="31" t="s">
         <v>415</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>416</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="26"/>
@@ -49504,13 +49501,13 @@
         <v>332</v>
       </c>
       <c r="B29" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="D29" s="31" t="s">
         <v>418</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>419</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="35"/>
@@ -49541,13 +49538,13 @@
         <v>335</v>
       </c>
       <c r="B30" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="31" t="s">
         <v>421</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>422</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="35"/>
@@ -49578,13 +49575,13 @@
         <v>338</v>
       </c>
       <c r="B31" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="D31" s="31" t="s">
         <v>424</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>425</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35"/>
@@ -49615,13 +49612,13 @@
         <v>341</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="D32" s="31" t="s">
         <v>427</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>428</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="35"/>
@@ -49652,13 +49649,13 @@
         <v>344</v>
       </c>
       <c r="B33" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="D33" s="31" t="s">
         <v>430</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>431</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="35"/>
@@ -49689,13 +49686,13 @@
         <v>347</v>
       </c>
       <c r="B34" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>432</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="D34" s="31" t="s">
         <v>433</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>434</v>
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="35"/>
@@ -55554,7 +55551,7 @@
         <v>146</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
@@ -55562,7 +55559,7 @@
         <v>146</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
@@ -55570,7 +55567,7 @@
         <v>146</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
@@ -55578,7 +55575,7 @@
         <v>164</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6">
@@ -55586,7 +55583,7 @@
         <v>170</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -55594,7 +55591,7 @@
         <v>170</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -55602,7 +55599,7 @@
         <v>170</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -55610,7 +55607,7 @@
         <v>189</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10">
@@ -55618,7 +55615,7 @@
         <v>196</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
@@ -55626,7 +55623,7 @@
         <v>200</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12">
@@ -55634,7 +55631,7 @@
         <v>204</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13">
@@ -55642,7 +55639,7 @@
         <v>332</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14">
@@ -55650,7 +55647,7 @@
         <v>335</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15">
@@ -55658,7 +55655,7 @@
         <v>338</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16">
@@ -55666,7 +55663,7 @@
         <v>341</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17">
@@ -55674,7 +55671,7 @@
         <v>344</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18">
@@ -55682,7 +55679,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -55723,7 +55720,7 @@
         <v>146</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3">
@@ -55731,7 +55728,7 @@
         <v>146</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
@@ -55739,7 +55736,7 @@
         <v>146</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5">
@@ -55747,7 +55744,7 @@
         <v>164</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6">
@@ -55755,7 +55752,7 @@
         <v>170</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7">
@@ -55763,7 +55760,7 @@
         <v>170</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -55771,7 +55768,7 @@
         <v>170</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -55779,7 +55776,7 @@
         <v>189</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10">
@@ -55787,7 +55784,7 @@
         <v>196</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11">
@@ -55795,7 +55792,7 @@
         <v>200</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12">
@@ -55803,7 +55800,7 @@
         <v>204</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13">
@@ -55811,7 +55808,7 @@
         <v>332</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14">
@@ -55819,7 +55816,7 @@
         <v>335</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15">
@@ -55827,7 +55824,7 @@
         <v>338</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16">
@@ -55835,7 +55832,7 @@
         <v>341</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17">
@@ -55843,7 +55840,7 @@
         <v>344</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18">
@@ -55851,7 +55848,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19">
@@ -58843,7 +58840,7 @@
         <v>146</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3">
@@ -58851,7 +58848,7 @@
         <v>146</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4">
@@ -58859,7 +58856,7 @@
         <v>146</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5">
@@ -58867,7 +58864,7 @@
         <v>164</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6">
@@ -58875,7 +58872,7 @@
         <v>170</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7">
@@ -58883,7 +58880,7 @@
         <v>170</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -58891,7 +58888,7 @@
         <v>170</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -58899,7 +58896,7 @@
         <v>189</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10">
@@ -58907,7 +58904,7 @@
         <v>196</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11">
@@ -58915,7 +58912,7 @@
         <v>200</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12">
@@ -58923,7 +58920,7 @@
         <v>204</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13">
@@ -58931,7 +58928,7 @@
         <v>332</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14">
@@ -58939,7 +58936,7 @@
         <v>335</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15">
@@ -58947,7 +58944,7 @@
         <v>338</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -58955,7 +58952,7 @@
         <v>341</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="17">
@@ -58963,7 +58960,7 @@
         <v>344</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18">
@@ -58971,7 +58968,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19">
@@ -61957,7 +61954,7 @@
         <v>146</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3">
@@ -61965,7 +61962,7 @@
         <v>146</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4">
@@ -61973,7 +61970,7 @@
         <v>146</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5">
@@ -61981,7 +61978,7 @@
         <v>164</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6">
@@ -61989,7 +61986,7 @@
         <v>170</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7">
@@ -61997,7 +61994,7 @@
         <v>170</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -62005,7 +62002,7 @@
         <v>170</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -62013,7 +62010,7 @@
         <v>189</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10">
@@ -62021,7 +62018,7 @@
         <v>196</v>
       </c>
       <c r="B10" s="48" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11">
@@ -62029,7 +62026,7 @@
         <v>200</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12">
@@ -62037,7 +62034,7 @@
         <v>204</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13">
@@ -62045,7 +62042,7 @@
         <v>332</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14">
@@ -62053,7 +62050,7 @@
         <v>335</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15">
@@ -62061,7 +62058,7 @@
         <v>338</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16">
@@ -62069,7 +62066,7 @@
         <v>341</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17">
@@ -62077,7 +62074,7 @@
         <v>344</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18">
@@ -62085,7 +62082,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
